--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A637B84E-340A-4753-AD62-6DC975105DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6673D37C-8D10-4150-9EE3-12DC24E1B113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1345,10 +1345,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3">
-        <v>420</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1489,7 +1489,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1644,10 +1644,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1667,10 +1667,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1759,10 +1759,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="G22" s="3">
-        <v>672</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1782,10 +1782,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G23" s="4">
-        <v>156</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1851,10 +1851,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1874,10 +1874,10 @@
         <v>7</v>
       </c>
       <c r="F27" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G27" s="4">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1920,10 +1920,10 @@
         <v>7</v>
       </c>
       <c r="F29" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2127,10 +2127,10 @@
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G38" s="3">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3116,10 +3116,10 @@
         <v>7</v>
       </c>
       <c r="F81" s="4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G81" s="4">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3139,10 +3139,10 @@
         <v>7</v>
       </c>
       <c r="F82" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G82" s="3">
-        <v>140</v>
+        <v>440</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3254,10 +3254,10 @@
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G87" s="4">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3323,10 +3323,10 @@
         <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G90" s="3">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3438,10 +3438,10 @@
         <v>11</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="4">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6673D37C-8D10-4150-9EE3-12DC24E1B113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4974FA-B6D6-4910-A51C-3EECB47F6593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1391,10 +1391,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3">
-        <v>322</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1414,10 +1414,10 @@
         <v>7</v>
       </c>
       <c r="F7" s="4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G7" s="4">
-        <v>294</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1483,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1644,10 +1644,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G17" s="4">
-        <v>500</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1667,10 +1667,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1736,10 +1736,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G21" s="4">
-        <v>780</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1759,10 +1759,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="G22" s="3">
-        <v>1392</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1782,10 +1782,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G23" s="4">
-        <v>348</v>
+        <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1805,10 +1805,10 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1851,10 +1851,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1874,10 +1874,10 @@
         <v>7</v>
       </c>
       <c r="F27" s="4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G27" s="4">
-        <v>192</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -2173,13 +2173,13 @@
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G40" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -2196,10 +2196,10 @@
         <v>7</v>
       </c>
       <c r="F41" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G41" s="4">
-        <v>168</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2317,7 +2317,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -2633,13 +2633,13 @@
         <v>7</v>
       </c>
       <c r="F60" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G60" s="3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2702,10 +2702,10 @@
         <v>7</v>
       </c>
       <c r="F63" s="4">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G63" s="4">
-        <v>320</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2777,7 +2777,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3116,10 +3116,10 @@
         <v>7</v>
       </c>
       <c r="F81" s="4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G81" s="4">
-        <v>680</v>
+        <v>540</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3139,10 +3139,10 @@
         <v>7</v>
       </c>
       <c r="F82" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G82" s="3">
-        <v>440</v>
+        <v>380</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3254,10 +3254,10 @@
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G87" s="4">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3323,10 +3323,10 @@
         <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G90" s="3">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3438,10 +3438,10 @@
         <v>11</v>
       </c>
       <c r="F95" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="4">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4974FA-B6D6-4910-A51C-3EECB47F6593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45ACE2CA-A69A-4A4A-AB3B-FB31E4C7B41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="106">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -337,6 +337,12 @@
   </si>
   <si>
     <t>HYUNDAI SERVO DEO ACEA C5-4 X 5 L</t>
+  </si>
+  <si>
+    <t>SERVO PREMIUM CF 4 15W 40-20L BUC</t>
+  </si>
+  <si>
+    <t>SERVO PREMIUM CF-4 15W-40-7.5 L</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491CF230-FE28-411F-9665-00F0E407DD20}">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
@@ -1368,10 +1374,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4">
-        <v>630</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1391,10 +1397,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3">
-        <v>182</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1506,10 +1512,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G11" s="4">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1644,10 +1650,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G17" s="4">
-        <v>410</v>
+        <v>810</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1667,10 +1673,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1713,10 +1719,10 @@
         <v>7</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G20" s="3">
-        <v>226.8</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1736,10 +1742,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G21" s="4">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1759,10 +1765,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G22" s="3">
-        <v>1104</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1782,10 +1788,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="4">
-        <v>720</v>
+        <v>708</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2058,10 +2064,10 @@
         <v>7</v>
       </c>
       <c r="F35" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2081,10 +2087,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G36" s="3">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2173,10 +2179,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G40" s="3">
-        <v>108</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2196,10 +2202,10 @@
         <v>7</v>
       </c>
       <c r="F41" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G41" s="4">
-        <v>126</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2242,10 +2248,10 @@
         <v>7</v>
       </c>
       <c r="F43" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" s="4">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2265,10 +2271,10 @@
         <v>7</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2288,10 +2294,10 @@
         <v>7</v>
       </c>
       <c r="F45" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" s="4">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2575,22 +2581,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>7577401</v>
+        <v>7577265</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="D58" s="3">
+        <v>6600</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2598,16 +2604,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="4">
-        <v>7577256</v>
+        <v>7577401</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D59" s="4">
-        <v>5025</v>
+        <v>59</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
@@ -2616,27 +2622,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>7577184</v>
+        <v>7577256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D60" s="3">
-        <v>6900</v>
+        <v>5025</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F60" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G60" s="3">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2644,22 +2650,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="4">
-        <v>7577174</v>
+        <v>7577184</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D61" s="4">
-        <v>7320</v>
+        <v>6900</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G61" s="4">
-        <v>120</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2667,22 +2673,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>7577234</v>
+        <v>7577174</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D62" s="3">
-        <v>6780</v>
+        <v>7320</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2690,10 +2696,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="4">
-        <v>7577240</v>
+        <v>7577234</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D63" s="4">
         <v>6780</v>
@@ -2702,33 +2708,33 @@
         <v>7</v>
       </c>
       <c r="F63" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G63" s="4">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>1404184</v>
+        <v>7577240</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D64" s="3">
-        <v>6800</v>
+        <v>6780</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F64" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G64" s="3">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -2736,22 +2742,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="4">
-        <v>1404184</v>
+        <v>7577251</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="D65" s="4">
-        <v>7100</v>
+        <v>2513</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" s="4">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2759,82 +2765,82 @@
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>1404234</v>
+        <v>1404184</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66" s="3">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G66" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="4">
-        <v>7436253</v>
+        <v>1404184</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D67" s="4">
-        <v>6175</v>
+        <v>7100</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>7436250</v>
+        <v>1404234</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D68" s="3">
-        <v>3113</v>
+        <v>7100</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F68" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4">
-        <v>7556234</v>
+        <v>7436253</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D69" s="4">
-        <v>6900</v>
+        <v>6175</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>7</v>
@@ -2846,18 +2852,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>7556184</v>
+        <v>7436250</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D70" s="3">
-        <v>7100</v>
+        <v>3113</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>7</v>
@@ -2874,13 +2880,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="4">
-        <v>7556241</v>
+        <v>7556234</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D71" s="4">
-        <v>3400</v>
+        <v>6900</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>7</v>
@@ -2897,13 +2903,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>7556253</v>
+        <v>7556184</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D72" s="3">
-        <v>5025</v>
+        <v>7100</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>7</v>
@@ -2920,36 +2926,36 @@
         <v>72</v>
       </c>
       <c r="B73" s="4">
-        <v>7556250</v>
+        <v>7556241</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D73" s="4">
-        <v>2563</v>
+        <v>3400</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F73" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" s="4">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>7489253</v>
+        <v>7556253</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D74" s="3">
-        <v>5675</v>
+        <v>5025</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>7</v>
@@ -2966,36 +2972,36 @@
         <v>74</v>
       </c>
       <c r="B75" s="4">
-        <v>7489265</v>
+        <v>7556250</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D75" s="4">
-        <v>7500</v>
+        <v>2563</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>7489184</v>
+        <v>7489253</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D76" s="3">
-        <v>7900</v>
+        <v>5675</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>7</v>
@@ -3007,18 +3013,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4">
-        <v>7489234</v>
+        <v>7489265</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D77" s="4">
-        <v>7700</v>
+        <v>7500</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>7</v>
@@ -3030,64 +3036,64 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>2889156</v>
+        <v>7489184</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D78" s="3">
-        <v>6840</v>
+        <v>7900</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G78" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4">
-        <v>7485242</v>
+        <v>7489234</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D79" s="4">
-        <v>2890</v>
+        <v>7700</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F79" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>7485265</v>
+        <v>2889156</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D80" s="3">
-        <v>5740</v>
+        <v>6840</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>7</v>
@@ -3096,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="G80" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -3104,22 +3110,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="4">
-        <v>7485184</v>
+        <v>7485242</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D81" s="4">
-        <v>6040</v>
+        <v>2890</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G81" s="4">
-        <v>540</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3127,22 +3133,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>7485174</v>
+        <v>7485265</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D82" s="3">
-        <v>6240</v>
+        <v>5740</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G82" s="3">
-        <v>380</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3150,22 +3156,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="4">
-        <v>7485234</v>
+        <v>7485184</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D83" s="4">
-        <v>6020</v>
+        <v>6040</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="4">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G83" s="4">
-        <v>200</v>
+        <v>540</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3173,22 +3179,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>7485251</v>
+        <v>7485174</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D84" s="3">
-        <v>2176</v>
+        <v>6240</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G84" s="3">
-        <v>22.5</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3196,22 +3202,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="4">
-        <v>7208271</v>
+        <v>7485234</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>10</v>
+        <v>81</v>
+      </c>
+      <c r="D85" s="4">
+        <v>6020</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F85" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G85" s="4">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3219,22 +3225,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>4906175</v>
+        <v>7485251</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D86" s="3">
-        <v>3960</v>
+        <v>2176</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G86" s="3">
-        <v>0</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3242,22 +3248,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="4">
-        <v>4906184</v>
+        <v>7208271</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D87" s="4">
-        <v>7500</v>
+        <v>83</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F87" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3265,22 +3271,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>7705451</v>
+        <v>4906175</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="D88" s="3">
+        <v>3960</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F88" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G88" s="3">
-        <v>546</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3288,22 +3294,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="4">
-        <v>7705339</v>
+        <v>4906184</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D89" s="4">
-        <v>2030</v>
+        <v>7500</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G89" s="4">
-        <v>15</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3311,22 +3317,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>7705341</v>
+        <v>7705451</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D90" s="3">
-        <v>8000</v>
+        <v>86</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F90" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3">
-        <v>80</v>
+        <v>546</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3334,22 +3340,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="4">
-        <v>7705337</v>
+        <v>7705339</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D91" s="4">
-        <v>4940</v>
+        <v>2030</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F91" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G91" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3357,22 +3363,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>3040265</v>
+        <v>7705341</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D92" s="3">
-        <v>4575</v>
+        <v>8000</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="3">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="G92" s="3">
-        <v>2040</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3380,22 +3386,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="4">
-        <v>3001265</v>
+        <v>7705337</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D93" s="4">
-        <v>5010</v>
+        <v>4940</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G93" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3403,22 +3409,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>3002265</v>
+        <v>3040265</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D94" s="3">
-        <v>5082</v>
+        <v>4575</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3426,16 +3432,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="4">
-        <v>3006401</v>
+        <v>3001265</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>10</v>
+        <v>91</v>
+      </c>
+      <c r="D95" s="4">
+        <v>5010</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F95" s="4">
         <v>0</v>
@@ -3449,22 +3455,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>3006265</v>
+        <v>3002265</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D96" s="3">
-        <v>5336</v>
+        <v>5082</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3472,10 +3478,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="4">
-        <v>3006403</v>
+        <v>3006401</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>10</v>
@@ -3495,22 +3501,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>3006234</v>
+        <v>3006265</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D98" s="3">
-        <v>5532</v>
+        <v>5336</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G98" s="3">
-        <v>280</v>
+        <v>340</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3518,10 +3524,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4">
-        <v>3084401</v>
+        <v>3006403</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>10</v>
@@ -3533,6 +3539,52 @@
         <v>0</v>
       </c>
       <c r="G99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3">
+        <v>3006234</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D100" s="3">
+        <v>5532</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" s="3">
+        <v>14</v>
+      </c>
+      <c r="G100" s="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4">
+        <v>3084401</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45ACE2CA-A69A-4A4A-AB3B-FB31E4C7B41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEACE1D-6185-4F18-A2DC-DDFFF4DE276D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="106">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -1254,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491CF230-FE28-411F-9665-00F0E407DD20}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
@@ -1397,10 +1397,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G6" s="3">
-        <v>616</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1512,10 +1512,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11" s="4">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1650,10 +1650,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="G17" s="4">
-        <v>810</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1673,10 +1673,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G18" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1742,10 +1742,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G21" s="4">
-        <v>620</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1765,10 +1765,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="G22" s="3">
-        <v>1212</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1926,10 +1926,10 @@
         <v>7</v>
       </c>
       <c r="F29" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="4">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2064,10 +2064,10 @@
         <v>7</v>
       </c>
       <c r="F35" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G35" s="4">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2087,10 +2087,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G36" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2162,27 +2162,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="3">
-        <v>2967204</v>
+        <v>7472184</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="3">
-        <v>6884</v>
+        <v>6500</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G40" s="3">
-        <v>144</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2190,45 +2190,45 @@
         <v>40</v>
       </c>
       <c r="B41" s="4">
-        <v>2967111</v>
+        <v>2967204</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D41" s="4">
-        <v>8020</v>
+        <v>6884</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F41" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G41" s="4">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>2502401</v>
+        <v>2967111</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8020</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F42" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G42" s="3">
-        <v>420</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2236,22 +2236,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="4">
-        <v>2502234</v>
+        <v>2502401</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D43" s="4">
-        <v>6980</v>
+        <v>45</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F43" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4">
-        <v>80</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2259,22 +2259,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>2502265</v>
+        <v>2502234</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="D44" s="3">
-        <v>6830</v>
+        <v>6980</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F44" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2282,22 +2282,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="4">
-        <v>2502184</v>
+        <v>2502265</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D45" s="4">
-        <v>7100</v>
+        <v>6830</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F45" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G45" s="4">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2305,68 +2305,68 @@
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>2502174</v>
+        <v>2502184</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D46" s="3">
-        <v>7520</v>
+        <v>7100</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F46" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G46" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="4">
-        <v>7511184</v>
+        <v>2502174</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" s="4">
-        <v>7800</v>
+        <v>7520</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F47" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G47" s="4">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="3">
-        <v>7511401</v>
+        <v>7511184</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="3">
         <v>10</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="3">
-        <v>2</v>
-      </c>
       <c r="G48" s="3">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2374,22 +2374,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="4">
-        <v>7511251</v>
+        <v>7511401</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="4">
-        <v>2763</v>
+        <v>50</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="4">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2397,22 +2397,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="3">
-        <v>7705313</v>
+        <v>7511251</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="D50" s="3">
-        <v>4500</v>
+        <v>2763</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F50" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G50" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2420,22 +2420,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="4">
-        <v>7705303</v>
+        <v>7705313</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" s="4">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F51" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G51" s="4">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2443,22 +2443,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>7211213</v>
+        <v>7705303</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D52" s="3">
-        <v>6300</v>
+        <v>4600</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2466,22 +2466,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="4">
-        <v>2927152</v>
+        <v>7211213</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="4">
-        <v>6840</v>
+        <v>6300</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F53" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="4">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2489,22 +2489,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>2933156</v>
+        <v>2927152</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="3">
-        <v>6480</v>
+        <v>6840</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F54" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G54" s="3">
-        <v>272</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2512,22 +2512,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="4">
-        <v>7584401</v>
+        <v>2933156</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
+      </c>
+      <c r="D55" s="4">
+        <v>6480</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F55" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G55" s="4">
-        <v>0</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2535,16 +2535,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>7584175</v>
+        <v>7584401</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="3">
-        <v>4060</v>
+        <v>56</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -2558,22 +2558,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="4">
-        <v>7584184</v>
+        <v>7584175</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="4">
-        <v>7400</v>
+        <v>4060</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G57" s="4">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2581,22 +2581,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>7577265</v>
+        <v>7584184</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D58" s="3">
-        <v>6600</v>
+        <v>7400</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G58" s="3">
-        <v>100</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2604,22 +2604,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="4">
-        <v>7577401</v>
+        <v>7577265</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="D59" s="4">
+        <v>6600</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F59" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G59" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2627,45 +2627,45 @@
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>7577256</v>
+        <v>7577401</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" s="3">
-        <v>5025</v>
+        <v>59</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="4">
-        <v>7577184</v>
+        <v>7577256</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D61" s="4">
-        <v>6900</v>
+        <v>5025</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G61" s="4">
-        <v>260</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2673,22 +2673,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>7577174</v>
+        <v>7577184</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D62" s="3">
-        <v>7320</v>
+        <v>6900</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F62" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G62" s="3">
-        <v>120</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2696,22 +2696,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="4">
-        <v>7577234</v>
+        <v>7577174</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D63" s="4">
-        <v>6780</v>
+        <v>7320</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F63" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G63" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2719,10 +2719,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>7577240</v>
+        <v>7577234</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D64" s="3">
         <v>6780</v>
@@ -2731,33 +2731,33 @@
         <v>7</v>
       </c>
       <c r="F64" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="4">
-        <v>7577251</v>
+        <v>7577240</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="D65" s="4">
-        <v>2513</v>
+        <v>6780</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G65" s="4">
-        <v>30</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2765,22 +2765,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>1404184</v>
+        <v>7577251</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="D66" s="3">
-        <v>6800</v>
+        <v>2513</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2794,16 +2794,16 @@
         <v>65</v>
       </c>
       <c r="D67" s="4">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2811,10 +2811,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>1404234</v>
+        <v>1404184</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D68" s="3">
         <v>7100</v>
@@ -2829,27 +2829,27 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4">
-        <v>7436253</v>
+        <v>1404234</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D69" s="4">
-        <v>6175</v>
+        <v>7100</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F69" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2857,13 +2857,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>7436250</v>
+        <v>7436253</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D70" s="3">
-        <v>3113</v>
+        <v>6175</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>7</v>
@@ -2875,18 +2875,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4">
-        <v>7556234</v>
+        <v>7436250</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D71" s="4">
-        <v>6900</v>
+        <v>3113</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>7</v>
@@ -2903,13 +2903,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>7556184</v>
+        <v>7556234</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D72" s="3">
-        <v>7100</v>
+        <v>6900</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>7</v>
@@ -2926,13 +2926,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="4">
-        <v>7556241</v>
+        <v>7556184</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D73" s="4">
-        <v>3400</v>
+        <v>7100</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>7</v>
@@ -2949,13 +2949,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>7556253</v>
+        <v>7556241</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D74" s="3">
-        <v>5025</v>
+        <v>3400</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>7</v>
@@ -2972,59 +2972,59 @@
         <v>74</v>
       </c>
       <c r="B75" s="4">
-        <v>7556250</v>
+        <v>7556253</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D75" s="4">
-        <v>2563</v>
+        <v>5025</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G75" s="4">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>7489253</v>
+        <v>7556250</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D76" s="3">
-        <v>5675</v>
+        <v>2563</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F76" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4">
-        <v>7489265</v>
+        <v>7489253</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D77" s="4">
-        <v>7500</v>
+        <v>5675</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>7</v>
@@ -3041,13 +3041,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>7489184</v>
+        <v>7489265</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D78" s="3">
-        <v>7900</v>
+        <v>7500</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>7</v>
@@ -3059,27 +3059,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4">
-        <v>7489234</v>
+        <v>7489184</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D79" s="4">
-        <v>7700</v>
+        <v>7900</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F79" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -3087,45 +3087,45 @@
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>2889156</v>
+        <v>7489234</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D80" s="3">
-        <v>6840</v>
+        <v>7700</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F80" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4">
-        <v>7485242</v>
+        <v>2889156</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D81" s="4">
-        <v>2890</v>
+        <v>6840</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G81" s="4">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3133,22 +3133,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>7485265</v>
+        <v>7485242</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D82" s="3">
-        <v>5740</v>
+        <v>2890</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" s="3">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3156,22 +3156,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="4">
-        <v>7485184</v>
+        <v>7485265</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D83" s="4">
-        <v>6040</v>
+        <v>5740</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="4">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G83" s="4">
-        <v>540</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3179,22 +3179,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>7485174</v>
+        <v>7485184</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" s="3">
-        <v>6240</v>
+        <v>6040</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="3">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G84" s="3">
-        <v>400</v>
+        <v>720</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3202,22 +3202,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="4">
-        <v>7485234</v>
+        <v>7485174</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D85" s="4">
-        <v>6020</v>
+        <v>6240</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F85" s="4">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G85" s="4">
-        <v>180</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3225,22 +3225,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>7485251</v>
+        <v>7485234</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D86" s="3">
-        <v>2176</v>
+        <v>6020</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G86" s="3">
-        <v>22.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3248,22 +3248,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="4">
-        <v>7208271</v>
+        <v>7485251</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="D87" s="4">
+        <v>2176</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G87" s="4">
-        <v>0</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3271,22 +3271,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>4906175</v>
+        <v>7208271</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D88" s="3">
-        <v>3960</v>
+        <v>83</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F88" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G88" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3294,22 +3294,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="4">
-        <v>4906184</v>
+        <v>4906175</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D89" s="4">
-        <v>7500</v>
+        <v>3960</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G89" s="4">
-        <v>280</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3317,22 +3317,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>7705451</v>
+        <v>4906184</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>10</v>
+        <v>85</v>
+      </c>
+      <c r="D90" s="3">
+        <v>7500</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G90" s="3">
-        <v>546</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3340,22 +3340,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="4">
-        <v>7705339</v>
+        <v>7705451</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D91" s="4">
-        <v>2030</v>
+        <v>86</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F91" s="4">
         <v>3</v>
       </c>
       <c r="G91" s="4">
-        <v>15</v>
+        <v>546</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3363,22 +3363,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>7705341</v>
+        <v>7705339</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D92" s="3">
-        <v>8000</v>
+        <v>2030</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G92" s="3">
-        <v>220</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3386,22 +3386,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="4">
-        <v>7705337</v>
+        <v>7705341</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D93" s="4">
-        <v>4940</v>
+        <v>8000</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G93" s="4">
-        <v>60</v>
+        <v>220</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3409,22 +3409,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>3040265</v>
+        <v>7705337</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D94" s="3">
-        <v>4575</v>
+        <v>4940</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F94" s="3">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="G94" s="3">
-        <v>1340</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3432,22 +3432,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="4">
-        <v>3001265</v>
+        <v>7705337</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D95" s="4">
-        <v>5010</v>
+        <v>4084</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -3455,22 +3455,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>3002265</v>
+        <v>3040265</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D96" s="3">
-        <v>5082</v>
+        <v>4575</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3478,16 +3478,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="4">
-        <v>3006401</v>
+        <v>3001265</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>10</v>
+        <v>91</v>
+      </c>
+      <c r="D97" s="4">
+        <v>5010</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F97" s="4">
         <v>0</v>
@@ -3501,22 +3501,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>3006265</v>
+        <v>3002265</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D98" s="3">
-        <v>5336</v>
+        <v>5082</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G98" s="3">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3524,10 +3524,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="4">
-        <v>3006403</v>
+        <v>3006401</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>10</v>
@@ -3547,22 +3547,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>3006234</v>
+        <v>3006265</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D100" s="3">
-        <v>5532</v>
+        <v>5336</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G100" s="3">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3570,10 +3570,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="4">
-        <v>3084401</v>
+        <v>3006403</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>10</v>
@@ -3585,6 +3585,52 @@
         <v>0</v>
       </c>
       <c r="G101" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3">
+        <v>3006234</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D102" s="3">
+        <v>5532</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" s="3">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4">
+        <v>3084401</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEACE1D-6185-4F18-A2DC-DDFFF4DE276D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C675E57-8F27-4E9F-A783-85FA8B6F817E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1328,10 +1328,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1397,10 +1397,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3">
-        <v>574</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1650,10 +1650,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="G17" s="4">
-        <v>560</v>
+        <v>960</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1742,10 +1742,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G21" s="4">
-        <v>700</v>
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1788,10 +1788,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G23" s="4">
-        <v>708</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1926,10 +1926,10 @@
         <v>7</v>
       </c>
       <c r="F29" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="4">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2064,10 +2064,10 @@
         <v>7</v>
       </c>
       <c r="F35" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G35" s="4">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2087,10 +2087,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G36" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2110,10 +2110,10 @@
         <v>7</v>
       </c>
       <c r="F37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2133,10 +2133,10 @@
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38" s="3">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2271,10 +2271,10 @@
         <v>7</v>
       </c>
       <c r="F44" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44" s="3">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2294,10 +2294,10 @@
         <v>7</v>
       </c>
       <c r="F45" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G45" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2317,10 +2317,10 @@
         <v>7</v>
       </c>
       <c r="F46" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G46" s="3">
-        <v>220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2593,10 +2593,10 @@
         <v>7</v>
       </c>
       <c r="F58" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G58" s="3">
-        <v>220</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2616,10 +2616,10 @@
         <v>7</v>
       </c>
       <c r="F59" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2639,10 +2639,10 @@
         <v>11</v>
       </c>
       <c r="F60" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="3">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2662,10 +2662,10 @@
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G61" s="4">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2685,10 +2685,10 @@
         <v>7</v>
       </c>
       <c r="F62" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G62" s="3">
-        <v>260</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2754,10 +2754,10 @@
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G65" s="4">
-        <v>380</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3168,10 +3168,10 @@
         <v>7</v>
       </c>
       <c r="F83" s="4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G83" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3191,10 +3191,10 @@
         <v>7</v>
       </c>
       <c r="F84" s="3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G84" s="3">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3214,10 +3214,10 @@
         <v>7</v>
       </c>
       <c r="F85" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G85" s="4">
-        <v>560</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3306,10 +3306,10 @@
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G89" s="4">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3329,10 +3329,10 @@
         <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G90" s="3">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3421,10 +3421,10 @@
         <v>7</v>
       </c>
       <c r="F94" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3467,10 +3467,10 @@
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G96" s="3">
-        <v>1340</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3559,10 +3559,10 @@
         <v>7</v>
       </c>
       <c r="F100" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C675E57-8F27-4E9F-A783-85FA8B6F817E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC767BB-848B-4654-9C55-C1B4B744FEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="109">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -343,6 +343,15 @@
   </si>
   <si>
     <t>SERVO PREMIUM CF-4 15W-40-7.5 L</t>
+  </si>
+  <si>
+    <t>S FLEET SUPREME CI4PLUS 15W-40-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVO FUTURA G PLUS 5W-30-20 X 1 L</t>
+  </si>
+  <si>
+    <t>SERVOSYSTEM 46 - 210L BRL</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491CF230-FE28-411F-9665-00F0E407DD20}">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
@@ -1328,10 +1337,10 @@
         <v>7</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1351,10 +1360,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3">
-        <v>840</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1374,10 +1383,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4">
-        <v>210</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1397,10 +1406,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3">
-        <v>490</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1420,10 +1429,10 @@
         <v>7</v>
       </c>
       <c r="F7" s="4">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G7" s="4">
-        <v>392</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1489,10 +1498,10 @@
         <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G10" s="3">
-        <v>196</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -1512,10 +1521,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G11" s="4">
-        <v>230</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1627,10 +1636,10 @@
         <v>7</v>
       </c>
       <c r="F16" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1650,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="G17" s="4">
-        <v>960</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1673,10 +1682,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1719,10 +1728,10 @@
         <v>7</v>
       </c>
       <c r="F20" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3">
-        <v>176.4</v>
+        <v>193.2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1742,10 +1751,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G21" s="4">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1765,10 +1774,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G22" s="3">
-        <v>1032</v>
+        <v>876</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1788,10 +1797,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G23" s="4">
-        <v>636</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1811,27 +1820,27 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>7470401</v>
+        <v>7470184</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>106</v>
+      </c>
+      <c r="D25" s="4">
+        <v>6700</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
@@ -1840,21 +1849,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3">
-        <v>2900145</v>
+        <v>7470401</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3">
-        <v>4600</v>
+        <v>29</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -1863,18 +1872,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4">
-        <v>2900125</v>
+        <v>2900145</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="4">
-        <v>5400</v>
+        <v>4600</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -1891,22 +1900,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="3">
-        <v>2900184</v>
+        <v>2900125</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="3">
-        <v>7140</v>
+        <v>5400</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F28" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1914,22 +1923,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>2900175</v>
+        <v>2900184</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="4">
-        <v>3760</v>
+        <v>7140</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" s="4">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1937,22 +1946,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="3">
-        <v>2900103</v>
+        <v>2900175</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="3">
-        <v>6600</v>
+        <v>3760</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F30" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G30" s="3">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1960,22 +1969,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="4">
-        <v>2924229</v>
+        <v>2900103</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D31" s="4">
-        <v>7600</v>
+        <v>6600</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1983,13 +1992,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3">
-        <v>2931184</v>
+        <v>2924229</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="D32" s="3">
-        <v>8700</v>
+        <v>7600</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>7</v>
@@ -2001,41 +2010,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4">
-        <v>2829230</v>
+        <v>2931184</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="D33" s="4">
-        <v>8440</v>
+        <v>8700</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="3">
-        <v>2828229</v>
+        <v>2829230</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D34" s="3">
-        <v>9280</v>
+        <v>8440</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>7</v>
@@ -2044,7 +2053,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="3">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2052,13 +2061,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4">
-        <v>2914175</v>
+        <v>2828229</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="4">
-        <v>6040</v>
+        <v>9280</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>7</v>
@@ -2075,45 +2084,45 @@
         <v>35</v>
       </c>
       <c r="B36" s="3">
-        <v>2914165</v>
+        <v>2914175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="3">
-        <v>3180</v>
+        <v>6040</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G36" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4">
-        <v>2909165</v>
+        <v>2914165</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" s="4">
-        <v>2200</v>
+        <v>3180</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F37" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G37" s="4">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2121,45 +2130,45 @@
         <v>37</v>
       </c>
       <c r="B38" s="3">
-        <v>2909175</v>
+        <v>2909165</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" s="3">
-        <v>4240</v>
+        <v>2200</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4">
-        <v>7472184</v>
+        <v>2909175</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D39" s="4">
-        <v>6380</v>
+        <v>4240</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F39" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2173,131 +2182,131 @@
         <v>42</v>
       </c>
       <c r="D40" s="3">
-        <v>6500</v>
+        <v>6380</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="4">
-        <v>2967204</v>
+        <v>7472184</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" s="4">
-        <v>6884</v>
+        <v>6500</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F41" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="3">
-        <v>2967111</v>
+        <v>2967184</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="D42" s="3">
-        <v>8020</v>
+        <v>11740</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F42" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="4">
-        <v>2502401</v>
+        <v>2967204</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="D43" s="4">
+        <v>6884</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F43" s="4">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G43" s="4">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="3">
-        <v>2502234</v>
+        <v>2967111</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D44" s="3">
-        <v>6980</v>
+        <v>8020</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F44" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G44" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="4">
-        <v>2502265</v>
+        <v>2967111</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="D45" s="4">
-        <v>6830</v>
+        <v>6372</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F45" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G45" s="4">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2305,22 +2314,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="3">
-        <v>2502184</v>
+        <v>2502401</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="3">
-        <v>7100</v>
+        <v>45</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F46" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3">
-        <v>140</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2328,45 +2337,45 @@
         <v>46</v>
       </c>
       <c r="B47" s="4">
-        <v>2502174</v>
+        <v>2502234</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D47" s="4">
-        <v>7520</v>
+        <v>6980</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F47" s="4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G47" s="4">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="3">
-        <v>7511184</v>
+        <v>2502265</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="D48" s="3">
-        <v>7800</v>
+        <v>6830</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F48" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2374,22 +2383,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="4">
-        <v>7511401</v>
+        <v>2502184</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="D49" s="4">
+        <v>7100</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F49" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G49" s="4">
-        <v>420</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2397,36 +2406,36 @@
         <v>49</v>
       </c>
       <c r="B50" s="3">
-        <v>7511251</v>
+        <v>2502174</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D50" s="3">
-        <v>2763</v>
+        <v>7520</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F50" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="4">
-        <v>7705313</v>
+        <v>7511184</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D51" s="4">
-        <v>4500</v>
+        <v>7800</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>7</v>
@@ -2435,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="G51" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2443,22 +2452,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="3">
-        <v>7705303</v>
+        <v>7511401</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="3">
-        <v>4600</v>
+        <v>50</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F52" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2466,13 +2475,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="4">
-        <v>7211213</v>
+        <v>7511251</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D53" s="4">
-        <v>6300</v>
+        <v>2763</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>7</v>
@@ -2489,22 +2498,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="3">
-        <v>2927152</v>
+        <v>7705313</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D54" s="3">
-        <v>6840</v>
+        <v>4500</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F54" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G54" s="3">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2512,22 +2521,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="4">
-        <v>2933156</v>
+        <v>7705303</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D55" s="4">
-        <v>6480</v>
+        <v>4600</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F55" s="4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G55" s="4">
-        <v>272</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2535,16 +2544,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="3">
-        <v>7584401</v>
+        <v>7211213</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>10</v>
+        <v>53</v>
+      </c>
+      <c r="D56" s="3">
+        <v>6300</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -2558,22 +2567,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="4">
-        <v>7584175</v>
+        <v>2927152</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D57" s="4">
-        <v>4060</v>
+        <v>6840</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="4">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2581,22 +2590,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="3">
-        <v>7584184</v>
+        <v>2933156</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D58" s="3">
-        <v>7400</v>
+        <v>6480</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G58" s="3">
-        <v>40</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2604,16 +2613,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="4">
-        <v>7577265</v>
+        <v>7584401</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59" s="4">
-        <v>6600</v>
+        <v>56</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
@@ -2627,16 +2636,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="3">
-        <v>7577401</v>
+        <v>7584175</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
+      </c>
+      <c r="D60" s="3">
+        <v>4060</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -2650,91 +2659,91 @@
         <v>60</v>
       </c>
       <c r="B61" s="4">
-        <v>7577256</v>
+        <v>7584184</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D61" s="4">
-        <v>5025</v>
+        <v>7400</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G61" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="3">
-        <v>7577184</v>
+        <v>7577265</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D62" s="3">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F62" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="4">
-        <v>7577174</v>
+        <v>7577401</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D63" s="4">
-        <v>7320</v>
+        <v>59</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F63" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G63" s="4">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="3">
-        <v>7577234</v>
+        <v>7577256</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D64" s="3">
-        <v>6780</v>
+        <v>5025</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F64" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -2742,91 +2751,91 @@
         <v>64</v>
       </c>
       <c r="B65" s="4">
-        <v>7577240</v>
+        <v>7577184</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D65" s="4">
-        <v>6780</v>
+        <v>6900</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G65" s="4">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="3">
-        <v>7577251</v>
+        <v>7577174</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="D66" s="3">
-        <v>2513</v>
+        <v>7320</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F66" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="4">
-        <v>1404184</v>
+        <v>7577234</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D67" s="4">
-        <v>6800</v>
+        <v>6780</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="3">
-        <v>1404184</v>
+        <v>7577240</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D68" s="3">
-        <v>7100</v>
+        <v>6780</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F68" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G68" s="3">
-        <v>60</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2834,36 +2843,36 @@
         <v>68</v>
       </c>
       <c r="B69" s="4">
-        <v>1404234</v>
+        <v>7577251</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D69" s="4">
-        <v>7100</v>
+        <v>2513</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F69" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="3">
-        <v>7436253</v>
+        <v>1404184</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D70" s="3">
-        <v>6175</v>
+        <v>6800</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>7</v>
@@ -2875,18 +2884,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4">
-        <v>7436250</v>
+        <v>1404184</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D71" s="4">
-        <v>3113</v>
+        <v>7100</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>7</v>
@@ -2903,13 +2912,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3">
-        <v>7556234</v>
+        <v>1404234</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D72" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>7</v>
@@ -2921,18 +2930,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="4">
-        <v>7556184</v>
+        <v>7436253</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="D73" s="4">
-        <v>7100</v>
+        <v>6175</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>7</v>
@@ -2944,18 +2953,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="3">
-        <v>7556241</v>
+        <v>7436250</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D74" s="3">
-        <v>3400</v>
+        <v>3113</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>7</v>
@@ -2972,22 +2981,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="4">
-        <v>7556253</v>
+        <v>7556234</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D75" s="4">
-        <v>5025</v>
+        <v>6900</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F75" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G75" s="4">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -2995,36 +3004,36 @@
         <v>75</v>
       </c>
       <c r="B76" s="3">
-        <v>7556250</v>
+        <v>7556184</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2563</v>
+        <v>7100</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F76" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" s="3">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4">
-        <v>7489253</v>
+        <v>7556241</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D77" s="4">
-        <v>5675</v>
+        <v>3400</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>7</v>
@@ -3041,22 +3050,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="3">
-        <v>7489265</v>
+        <v>7556253</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D78" s="3">
-        <v>7500</v>
+        <v>5025</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G78" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3064,22 +3073,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="4">
-        <v>7489184</v>
+        <v>7556250</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D79" s="4">
-        <v>7900</v>
+        <v>2563</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F79" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="4">
-        <v>40</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
@@ -3087,13 +3096,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="3">
-        <v>7489234</v>
+        <v>7489253</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D80" s="3">
-        <v>7700</v>
+        <v>5675</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>7</v>
@@ -3105,27 +3114,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4">
-        <v>2889156</v>
+        <v>7489265</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D81" s="4">
-        <v>6840</v>
+        <v>7500</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3133,36 +3142,36 @@
         <v>81</v>
       </c>
       <c r="B82" s="3">
-        <v>7485242</v>
+        <v>7489184</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D82" s="3">
-        <v>2890</v>
+        <v>7900</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
       <c r="B83" s="4">
-        <v>7485265</v>
+        <v>7489234</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D83" s="4">
-        <v>5740</v>
+        <v>7700</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>7</v>
@@ -3174,27 +3183,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="3">
-        <v>7485184</v>
+        <v>2889156</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D84" s="3">
-        <v>6040</v>
+        <v>6840</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G84" s="3">
-        <v>500</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3202,22 +3211,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="4">
-        <v>7485174</v>
+        <v>7485242</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D85" s="4">
-        <v>6240</v>
+        <v>2890</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F85" s="4">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G85" s="4">
-        <v>480</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3225,22 +3234,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="3">
-        <v>7485234</v>
+        <v>7485265</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D86" s="3">
-        <v>6020</v>
+        <v>5740</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F86" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G86" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3248,22 +3257,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="4">
-        <v>7485251</v>
+        <v>7485184</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D87" s="4">
-        <v>2176</v>
+        <v>6040</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G87" s="4">
-        <v>22.5</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3271,22 +3280,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="3">
-        <v>7208271</v>
+        <v>7485174</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="D88" s="3">
+        <v>6240</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F88" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G88" s="3">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3294,22 +3303,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="4">
-        <v>4906175</v>
+        <v>7485234</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D89" s="4">
-        <v>3960</v>
+        <v>6020</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G89" s="4">
-        <v>20</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3317,22 +3326,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="3">
-        <v>4906184</v>
+        <v>7485251</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D90" s="3">
-        <v>7500</v>
+        <v>2176</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3340,10 +3349,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="4">
-        <v>7705451</v>
+        <v>7208271</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>10</v>
@@ -3352,10 +3361,10 @@
         <v>11</v>
       </c>
       <c r="F91" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G91" s="4">
-        <v>546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3363,22 +3372,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="3">
-        <v>7705339</v>
+        <v>4906175</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D92" s="3">
-        <v>2030</v>
+        <v>3960</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F92" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G92" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3386,22 +3395,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="4">
-        <v>7705341</v>
+        <v>4906184</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D93" s="4">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F93" s="4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G93" s="4">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3409,22 +3418,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="3">
-        <v>7705337</v>
+        <v>7705451</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" s="3">
-        <v>4940</v>
+        <v>86</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>546</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3432,22 +3441,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="4">
-        <v>7705337</v>
+        <v>7705339</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D95" s="4">
-        <v>4084</v>
+        <v>2030</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F95" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -3455,22 +3464,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>3040265</v>
+        <v>7705341</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D96" s="3">
-        <v>4575</v>
+        <v>8000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="G96" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3478,13 +3487,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4">
-        <v>3001265</v>
+        <v>7705337</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D97" s="4">
-        <v>5010</v>
+        <v>4940</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>7</v>
@@ -3501,13 +3510,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>3002265</v>
+        <v>7705337</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D98" s="3">
-        <v>5082</v>
+        <v>4084</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>7</v>
@@ -3524,22 +3533,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="4">
-        <v>3006401</v>
+        <v>3040265</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>10</v>
+        <v>90</v>
+      </c>
+      <c r="D99" s="4">
+        <v>4575</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F99" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G99" s="4">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3547,13 +3556,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>3006265</v>
+        <v>3001265</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D100" s="3">
-        <v>5336</v>
+        <v>5010</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>7</v>
@@ -3570,16 +3579,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="4">
-        <v>3006403</v>
+        <v>3002265</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>10</v>
+        <v>102</v>
+      </c>
+      <c r="D101" s="4">
+        <v>5082</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F101" s="4">
         <v>0</v>
@@ -3593,22 +3602,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="3">
-        <v>3006234</v>
+        <v>3002401</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D102" s="3">
-        <v>5532</v>
+        <v>108</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F102" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -3616,10 +3625,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="4">
-        <v>3084401</v>
+        <v>3006401</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>10</v>
@@ -3631,6 +3640,98 @@
         <v>0</v>
       </c>
       <c r="G103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3">
+        <v>3006265</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D104" s="3">
+        <v>5336</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4">
+        <v>3006403</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3">
+        <v>3006234</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D106" s="3">
+        <v>5532</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" s="3">
+        <v>6</v>
+      </c>
+      <c r="G106" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4">
+        <v>3084401</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC767BB-848B-4654-9C55-C1B4B744FEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90924DED-6689-4472-9796-1B4C9C60D740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1360,10 +1360,10 @@
         <v>11</v>
       </c>
       <c r="F4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1406,10 +1406,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1429,10 +1429,10 @@
         <v>7</v>
       </c>
       <c r="F7" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>210</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1498,13 +1498,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1521,10 +1521,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G11" s="4">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1550,7 +1550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1659,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G17" s="4">
-        <v>310</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1682,10 +1682,10 @@
         <v>7</v>
       </c>
       <c r="F18" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G18" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1751,10 +1751,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1774,10 +1774,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G22" s="3">
-        <v>876</v>
+        <v>828</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1797,10 +1797,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G23" s="4">
-        <v>408</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1820,13 +1820,13 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G24" s="3">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1866,13 +1866,13 @@
         <v>11</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -1889,10 +1889,10 @@
         <v>7</v>
       </c>
       <c r="F27" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="4">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1912,10 +1912,10 @@
         <v>7</v>
       </c>
       <c r="F28" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G28" s="3">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1935,10 +1935,10 @@
         <v>7</v>
       </c>
       <c r="F29" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="4">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1958,10 +1958,10 @@
         <v>7</v>
       </c>
       <c r="F30" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1981,10 +1981,10 @@
         <v>7</v>
       </c>
       <c r="F31" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2004,10 +2004,10 @@
         <v>7</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2050,10 +2050,10 @@
         <v>7</v>
       </c>
       <c r="F34" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="3">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2096,10 +2096,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G36" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2119,13 +2119,13 @@
         <v>7</v>
       </c>
       <c r="F37" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G37" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2142,13 +2142,13 @@
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2165,10 +2165,10 @@
         <v>7</v>
       </c>
       <c r="F39" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G39" s="4">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2188,10 +2188,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G40" s="3">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2240,7 +2240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2257,13 +2257,13 @@
         <v>7</v>
       </c>
       <c r="F43" s="4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G43" s="4">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -2280,13 +2280,13 @@
         <v>7</v>
       </c>
       <c r="F44" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G44" s="3">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2349,10 +2349,10 @@
         <v>7</v>
       </c>
       <c r="F47" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G47" s="4">
-        <v>260</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2395,10 +2395,10 @@
         <v>7</v>
       </c>
       <c r="F49" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G49" s="4">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2424,7 +2424,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2510,10 +2510,10 @@
         <v>7</v>
       </c>
       <c r="F54" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G54" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2602,10 +2602,10 @@
         <v>7</v>
       </c>
       <c r="F58" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G58" s="3">
-        <v>112</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2648,10 +2648,10 @@
         <v>7</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2671,10 +2671,10 @@
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G61" s="4">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2717,10 +2717,10 @@
         <v>11</v>
       </c>
       <c r="F63" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="4">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2740,13 +2740,13 @@
         <v>7</v>
       </c>
       <c r="F64" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G64" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2809,13 +2809,13 @@
         <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2832,10 +2832,10 @@
         <v>7</v>
       </c>
       <c r="F68" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G68" s="3">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3062,10 +3062,10 @@
         <v>7</v>
       </c>
       <c r="F78" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G78" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3091,7 +3091,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -3200,10 +3200,10 @@
         <v>7</v>
       </c>
       <c r="F84" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G84" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3269,10 +3269,10 @@
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G87" s="4">
-        <v>500</v>
+        <v>940</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3292,10 +3292,10 @@
         <v>7</v>
       </c>
       <c r="F88" s="3">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G88" s="3">
-        <v>360</v>
+        <v>660</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3315,10 +3315,10 @@
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G89" s="4">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3338,10 +3338,10 @@
         <v>7</v>
       </c>
       <c r="F90" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G90" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3384,10 +3384,10 @@
         <v>7</v>
       </c>
       <c r="F92" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G92" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3407,10 +3407,10 @@
         <v>7</v>
       </c>
       <c r="F93" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" s="4">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3476,10 +3476,10 @@
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G96" s="3">
-        <v>200</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3545,10 +3545,10 @@
         <v>7</v>
       </c>
       <c r="F99" s="4">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G99" s="4">
-        <v>2000</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3706,10 +3706,10 @@
         <v>7</v>
       </c>
       <c r="F106" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G106" s="3">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90924DED-6689-4472-9796-1B4C9C60D740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7F1F43-AB03-414D-9D1C-57AA0720B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1383,10 +1383,10 @@
         <v>11</v>
       </c>
       <c r="F5" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1504,7 +1504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1751,10 +1751,10 @@
         <v>7</v>
       </c>
       <c r="F21" s="4">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G21" s="4">
-        <v>800</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1774,10 +1774,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3">
-        <v>828</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1820,13 +1820,13 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G24" s="3">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -1889,10 +1889,10 @@
         <v>7</v>
       </c>
       <c r="F27" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="4">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1912,10 +1912,10 @@
         <v>7</v>
       </c>
       <c r="F28" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G28" s="3">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1958,10 +1958,10 @@
         <v>7</v>
       </c>
       <c r="F30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2004,10 +2004,10 @@
         <v>7</v>
       </c>
       <c r="F32" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2096,10 +2096,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G36" s="3">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2119,13 +2119,13 @@
         <v>7</v>
       </c>
       <c r="F37" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G37" s="4">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2142,13 +2142,13 @@
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2165,10 +2165,10 @@
         <v>7</v>
       </c>
       <c r="F39" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G39" s="4">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2188,10 +2188,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G40" s="3">
-        <v>360</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2240,7 +2240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2349,10 +2349,10 @@
         <v>7</v>
       </c>
       <c r="F47" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G47" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2395,10 +2395,10 @@
         <v>7</v>
       </c>
       <c r="F49" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G49" s="4">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2424,7 +2424,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2648,10 +2648,10 @@
         <v>7</v>
       </c>
       <c r="F60" s="3">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G60" s="3">
-        <v>410</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2671,10 +2671,10 @@
         <v>7</v>
       </c>
       <c r="F61" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G61" s="4">
-        <v>200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2740,13 +2740,13 @@
         <v>7</v>
       </c>
       <c r="F64" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2763,13 +2763,13 @@
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2809,13 +2809,13 @@
         <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -3223,10 +3223,10 @@
         <v>7</v>
       </c>
       <c r="F85" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G85" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3269,10 +3269,10 @@
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G87" s="4">
-        <v>940</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3292,10 +3292,10 @@
         <v>7</v>
       </c>
       <c r="F88" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G88" s="3">
-        <v>660</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3315,10 +3315,10 @@
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G89" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3384,10 +3384,10 @@
         <v>7</v>
       </c>
       <c r="F92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3407,10 +3407,10 @@
         <v>7</v>
       </c>
       <c r="F93" s="4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G93" s="4">
-        <v>320</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3430,10 +3430,10 @@
         <v>11</v>
       </c>
       <c r="F94" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
-        <v>546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3476,10 +3476,10 @@
         <v>7</v>
       </c>
       <c r="F96" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G96" s="3">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3545,10 +3545,10 @@
         <v>7</v>
       </c>
       <c r="F99" s="4">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="G99" s="4">
-        <v>2140</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3706,10 +3706,10 @@
         <v>7</v>
       </c>
       <c r="F106" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G106" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7F1F43-AB03-414D-9D1C-57AA0720B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCAA41-87A2-456D-9C8B-01F860076800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="114">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -352,6 +352,21 @@
   </si>
   <si>
     <t>SERVOSYSTEM 46 - 210L BRL</t>
+  </si>
+  <si>
+    <t>SERVO SUPER 20W-40 MG-210 L BRL</t>
+  </si>
+  <si>
+    <t>SERVOGEM EP 2-182 KG DRM</t>
+  </si>
+  <si>
+    <t>SERVOGEM EP 2-20 KG BUC</t>
+  </si>
+  <si>
+    <t>SERVOMESH SP 220 - 210L BRL</t>
+  </si>
+  <si>
+    <t>SERVOMESH SP 320 - 210L BRL</t>
   </si>
 </sst>
 </file>
@@ -518,18 +533,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6E6FA"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -705,8 +708,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6FA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -849,6 +864,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -857,44 +896,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -902,10 +941,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1263,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491CF230-FE28-411F-9665-00F0E407DD20}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" customWidth="1"/>
@@ -1301,45 +1346,45 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>7271111</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <v>6240</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="6">
         <v>7271111</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6">
         <v>10080</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6">
         <v>1</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="6">
         <v>14</v>
       </c>
     </row>
@@ -1347,45 +1392,45 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>7079401</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="6">
         <v>7427401</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1393,45 +1438,45 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>7427213</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>6456</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4">
         <v>16</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="6">
         <v>7420213</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="6">
         <v>6300</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="E7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1439,45 +1484,45 @@
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>7420213</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>5812</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="E8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="6">
         <v>7209213</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="6">
         <v>15540</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="E9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1485,91 +1530,91 @@
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>2968213</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>6008</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="6">
         <v>2557195</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>4200</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4">
-        <v>9</v>
-      </c>
-      <c r="G11" s="4">
-        <v>90</v>
+      <c r="E11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6">
+        <v>6</v>
+      </c>
+      <c r="G11" s="6">
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>7232184</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>6020</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4">
         <v>5</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>7638234</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>8400</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6">
         <v>1</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="6">
         <v>20</v>
       </c>
     </row>
@@ -1577,45 +1622,45 @@
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>7638234</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>7800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="6">
         <v>7421234</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="6">
         <v>9600</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="E15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1623,45 +1668,45 @@
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>7205222</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>6880</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="E16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="6">
         <v>7330242</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="6">
         <v>670</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="E17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6">
         <v>39</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="6">
         <v>390</v>
       </c>
     </row>
@@ -1669,45 +1714,45 @@
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>7330265</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>1300</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="E18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="4">
         <v>20</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="6">
         <v>7670213</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="6">
         <v>4860</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="4">
+      <c r="E19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="6">
         <v>5</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="6">
         <v>70</v>
       </c>
     </row>
@@ -1715,137 +1760,137 @@
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>2540199</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>3000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="3">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3">
-        <v>193.2</v>
+      <c r="E20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4">
+        <v>18</v>
+      </c>
+      <c r="G20" s="4">
+        <v>151.19999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="6">
         <v>7600184</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="6">
         <v>6780</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="4">
-        <v>29</v>
-      </c>
-      <c r="G21" s="4">
-        <v>580</v>
+      <c r="E21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="6">
+        <v>26</v>
+      </c>
+      <c r="G21" s="6">
+        <v>520</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>7600203</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>4068</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="3">
-        <v>37</v>
-      </c>
-      <c r="G22" s="3">
-        <v>444</v>
+      <c r="E22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="4">
+        <v>71</v>
+      </c>
+      <c r="G22" s="4">
+        <v>852</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="6">
         <v>7688203</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="6">
         <v>4308</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="4">
-        <v>53</v>
-      </c>
-      <c r="G23" s="4">
-        <v>636</v>
+      <c r="E23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="6">
+        <v>52</v>
+      </c>
+      <c r="G23" s="6">
+        <v>624</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>7688213</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>5028</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="3">
-        <v>7</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="4">
+        <v>7</v>
+      </c>
+      <c r="G24" s="4">
         <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="6">
         <v>7470184</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="6">
         <v>6700</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="4">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="E25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1853,183 +1898,183 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>7470401</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="4">
         <v>1</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="4">
         <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="6">
         <v>2900145</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="6">
         <v>4600</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="4">
-        <v>4</v>
-      </c>
-      <c r="G27" s="4">
-        <v>48</v>
+      <c r="E27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="6">
+        <v>38</v>
+      </c>
+      <c r="G27" s="6">
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>2900125</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="4">
         <v>5400</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="4">
         <v>6</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="4">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="6">
         <v>2900184</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="6">
         <v>7140</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="4">
-        <v>5</v>
-      </c>
-      <c r="G29" s="4">
-        <v>100</v>
+      <c r="E29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="6">
+        <v>2</v>
+      </c>
+      <c r="G29" s="6">
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="4">
         <v>2900175</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="4">
         <v>3760</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="4">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4">
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="6">
         <v>2900103</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="6">
         <v>6600</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="4">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4">
-        <v>0</v>
+      <c r="E31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="6">
+        <v>1</v>
+      </c>
+      <c r="G31" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="4">
         <v>2924229</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="4">
         <v>7600</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4">
         <v>1</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="6">
         <v>2931184</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="6">
         <v>8700</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="E33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2037,45 +2082,45 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="4">
         <v>2829230</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <v>8440</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="4">
         <v>2</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="4">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="6">
         <v>2828229</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="6">
         <v>9280</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="E35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2083,91 +2128,91 @@
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="4">
         <v>2914175</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>6040</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="3">
-        <v>4</v>
-      </c>
-      <c r="G36" s="3">
-        <v>40</v>
+      <c r="E36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="4">
+        <v>7</v>
+      </c>
+      <c r="G36" s="4">
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="6">
         <v>2914165</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="6">
         <v>3180</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="4">
-        <v>2</v>
-      </c>
-      <c r="G37" s="4">
-        <v>10</v>
+      <c r="E37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="6">
+        <v>5</v>
+      </c>
+      <c r="G37" s="6">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="4">
         <v>2909165</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="4">
         <v>2200</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="E38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="6">
         <v>2909175</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="6">
         <v>4240</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="4">
+      <c r="E39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="6">
         <v>6</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="6">
         <v>60</v>
       </c>
     </row>
@@ -2175,45 +2220,45 @@
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="4">
         <v>7472184</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>6380</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="3">
-        <v>13</v>
-      </c>
-      <c r="G40" s="3">
-        <v>260</v>
+      <c r="E40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="4">
+        <v>7</v>
+      </c>
+      <c r="G40" s="4">
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="6">
         <v>7472184</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="6">
         <v>6500</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="4">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4">
+      <c r="E41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2221,45 +2266,45 @@
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="4">
         <v>2967184</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="4">
         <v>11740</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="E42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4">
         <v>1</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="4">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="6">
         <v>2967204</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="6">
         <v>6884</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="4">
+      <c r="E43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="6">
         <v>21</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="6">
         <v>252</v>
       </c>
     </row>
@@ -2267,45 +2312,45 @@
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="4">
         <v>2967111</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="4">
         <v>8020</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="3">
-        <v>7</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="E44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="4">
+        <v>7</v>
+      </c>
+      <c r="G44" s="4">
         <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="6">
         <v>2967111</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="6">
         <v>6372</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="E45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="6">
         <v>10</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="6">
         <v>140</v>
       </c>
     </row>
@@ -2313,45 +2358,45 @@
       <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="4">
         <v>2502401</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="4">
         <v>2</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="4">
         <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="6">
         <v>2502234</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="6">
         <v>6980</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="4">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="E47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2359,137 +2404,137 @@
       <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="4">
         <v>2502265</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="4">
         <v>6830</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
+      <c r="E48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="4">
+        <v>3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="6">
         <v>2502184</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="6">
         <v>7100</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" s="4">
-        <v>12</v>
-      </c>
-      <c r="G49" s="4">
-        <v>240</v>
+      <c r="E49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="6">
+        <v>15</v>
+      </c>
+      <c r="G49" s="6">
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="4">
         <v>2502174</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="4">
         <v>7520</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="3">
+      <c r="E50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="4">
         <v>6</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="4">
         <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="6">
         <v>7511184</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="6">
         <v>7800</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" s="4">
-        <v>10</v>
-      </c>
-      <c r="G51" s="4">
-        <v>200</v>
+      <c r="E51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="6">
+        <v>7</v>
+      </c>
+      <c r="G51" s="6">
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="4">
         <v>7511401</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="F52" s="4">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="6">
         <v>7511251</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="6">
         <v>2763</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="4">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="E53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2497,45 +2542,45 @@
       <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="4">
         <v>7705313</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="4">
         <v>4500</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="E54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="4">
         <v>8</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="4">
         <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="6">
         <v>7705303</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="6">
         <v>4600</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="4">
+      <c r="E55" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="6">
         <v>6</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="6">
         <v>60</v>
       </c>
     </row>
@@ -2543,45 +2588,45 @@
       <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>7211213</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="4">
         <v>6300</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="3">
+      <c r="E56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="4">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="6">
         <v>2927152</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="6">
         <v>6840</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="4">
+      <c r="E57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="6">
         <v>2</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="6">
         <v>36</v>
       </c>
     </row>
@@ -2589,45 +2634,45 @@
       <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>2933156</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="4">
         <v>6480</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="E58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="4">
         <v>4</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="4">
         <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="6">
         <v>7584401</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="4">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4">
+      <c r="F59" s="6">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2635,183 +2680,183 @@
       <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>7584175</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="4">
         <v>4060</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="3">
-        <v>28</v>
-      </c>
-      <c r="G60" s="3">
-        <v>280</v>
+      <c r="E60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="4">
+        <v>25</v>
+      </c>
+      <c r="G60" s="4">
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="6">
         <v>7584184</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="6">
         <v>7400</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="4">
-        <v>3</v>
-      </c>
-      <c r="G61" s="4">
-        <v>60</v>
+      <c r="E61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="6">
+        <v>11</v>
+      </c>
+      <c r="G61" s="6">
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="4">
         <v>7577265</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="4">
         <v>6600</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="E62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="4">
+        <v>0</v>
+      </c>
+      <c r="G62" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="6">
         <v>7577401</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F63" s="4">
-        <v>1</v>
-      </c>
-      <c r="G63" s="4">
-        <v>210</v>
+      <c r="F63" s="6">
+        <v>3</v>
+      </c>
+      <c r="G63" s="6">
+        <v>630</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>7577256</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="4">
         <v>5025</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="3">
+      <c r="E64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="4">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="6">
         <v>7577184</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="6">
         <v>6900</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" s="4">
-        <v>2</v>
-      </c>
-      <c r="G65" s="4">
-        <v>40</v>
+      <c r="E65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" s="6">
+        <v>7</v>
+      </c>
+      <c r="G65" s="6">
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>7577174</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="4">
         <v>7320</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="E66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="4">
         <v>5</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="4">
         <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="6">
         <v>7577234</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="6">
         <v>6780</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" s="4">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4">
+      <c r="E67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2819,45 +2864,45 @@
       <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>7577240</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="4">
         <v>6780</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="3">
+      <c r="E68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="4">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="6">
         <v>7577251</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="6">
         <v>2513</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" s="4">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4">
+      <c r="E69" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2865,91 +2910,91 @@
       <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>1404184</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="4">
         <v>6800</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="3">
+      <c r="E70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" s="4">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="6">
         <v>1404184</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="6">
         <v>7100</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="4">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4">
-        <v>0</v>
+      <c r="E71" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="6">
+        <v>2</v>
+      </c>
+      <c r="G71" s="6">
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="4">
         <v>1404234</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="4">
         <v>7100</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="E72" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F72" s="4">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="6">
         <v>7436253</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="6">
         <v>6175</v>
       </c>
-      <c r="E73" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" s="4">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4">
+      <c r="E73" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2957,45 +3002,45 @@
       <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="4">
         <v>7436250</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="4">
         <v>3113</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" s="3">
-        <v>0</v>
-      </c>
-      <c r="G74" s="3">
+      <c r="E74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" s="4">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="6">
         <v>7556234</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="6">
         <v>6900</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="4">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4">
+      <c r="E75" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3003,45 +3048,45 @@
       <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="4">
         <v>7556184</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="4">
         <v>7100</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="E76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" s="4">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="6">
         <v>7556241</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="6">
         <v>3400</v>
       </c>
-      <c r="E77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" s="4">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
+      <c r="E77" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" s="6">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3049,45 +3094,45 @@
       <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="4">
         <v>7556253</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="4">
         <v>5025</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" s="3">
-        <v>0</v>
-      </c>
-      <c r="G78" s="3">
+      <c r="E78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F78" s="4">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="6">
         <v>7556250</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="6">
         <v>2563</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" s="4">
+      <c r="E79" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F79" s="6">
         <v>3</v>
       </c>
-      <c r="G79" s="4">
+      <c r="G79" s="6">
         <v>22.5</v>
       </c>
     </row>
@@ -3095,45 +3140,45 @@
       <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="4">
         <v>7489253</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="4">
         <v>5675</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" s="3">
-        <v>0</v>
-      </c>
-      <c r="G80" s="3">
+      <c r="E80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F80" s="4">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="6">
         <v>7489265</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="6">
         <v>7500</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" s="4">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4">
+      <c r="E81" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F81" s="6">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3141,45 +3186,45 @@
       <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="4">
         <v>7489184</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="4">
         <v>7900</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" s="3">
-        <v>0</v>
-      </c>
-      <c r="G82" s="3">
+      <c r="E82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="4">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="6">
         <v>7489234</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="6">
         <v>7700</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" s="4">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4">
+      <c r="E83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3187,413 +3232,413 @@
       <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="4">
         <v>2889156</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="4">
         <v>6840</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" s="3">
-        <v>0</v>
-      </c>
-      <c r="G84" s="3">
-        <v>0</v>
+      <c r="E84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" s="4">
+        <v>3</v>
+      </c>
+      <c r="G84" s="4">
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="6">
         <v>7485242</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="6">
         <v>2890</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" s="4">
-        <v>3</v>
-      </c>
-      <c r="G85" s="4">
-        <v>30</v>
+      <c r="E85" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="4">
         <v>7485265</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="4">
         <v>5740</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" s="3">
-        <v>0</v>
-      </c>
-      <c r="G86" s="3">
-        <v>0</v>
+      <c r="E86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" s="4">
+        <v>3</v>
+      </c>
+      <c r="G86" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="6">
         <v>7485184</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="6">
         <v>6040</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" s="4">
-        <v>26</v>
-      </c>
-      <c r="G87" s="4">
-        <v>520</v>
+      <c r="E87" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" s="6">
+        <v>13</v>
+      </c>
+      <c r="G87" s="6">
+        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="4">
+        <v>7485401</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="4">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="5">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6">
         <v>7485174</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C89" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D89" s="6">
         <v>6240</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" s="3">
-        <v>25</v>
-      </c>
-      <c r="G88" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
-        <v>88</v>
-      </c>
-      <c r="B89" s="4">
-        <v>7485234</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" s="4">
-        <v>6020</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" s="4">
-        <v>0</v>
-      </c>
-      <c r="G89" s="4">
-        <v>0</v>
+      <c r="E89" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F89" s="6">
+        <v>22</v>
+      </c>
+      <c r="G89" s="6">
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="4">
+        <v>7485234</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D90" s="4">
+        <v>6020</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F90" s="4">
+        <v>5</v>
+      </c>
+      <c r="G90" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="5">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6">
         <v>7485251</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C91" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D91" s="6">
         <v>2176</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" s="3">
+      <c r="E91" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" s="6">
         <v>6</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G91" s="6">
         <v>45</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
-        <v>90</v>
-      </c>
-      <c r="B91" s="4">
-        <v>7208271</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="4">
-        <v>0</v>
-      </c>
-      <c r="G91" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="4">
+        <v>7208271</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="4">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="5">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6">
         <v>4906175</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C93" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D93" s="6">
         <v>3960</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" s="3">
-        <v>0</v>
-      </c>
-      <c r="G92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
-        <v>92</v>
-      </c>
-      <c r="B93" s="4">
-        <v>4906184</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D93" s="4">
-        <v>7500</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" s="4">
-        <v>4</v>
-      </c>
-      <c r="G93" s="4">
-        <v>80</v>
+      <c r="E93" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" s="6">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" s="3">
-        <v>7705451</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D94" s="3" t="s">
+      <c r="B94" s="4">
+        <v>4906184</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D94" s="4">
+        <v>7500</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F94" s="4">
+        <v>4</v>
+      </c>
+      <c r="G94" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="5">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6">
+        <v>7742451</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E95" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
-        <v>94</v>
-      </c>
-      <c r="B95" s="4">
-        <v>7705339</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D95" s="4">
-        <v>2030</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-      <c r="G95" s="4">
-        <v>0</v>
+      <c r="F95" s="6">
+        <v>1</v>
+      </c>
+      <c r="G95" s="6">
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" s="3">
-        <v>7705341</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D96" s="3">
-        <v>8000</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" s="3">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3">
-        <v>80</v>
+      <c r="B96" s="4">
+        <v>7742341</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="4">
+        <v>9700</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" s="4">
+        <v>15</v>
+      </c>
+      <c r="G96" s="4">
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="4">
-        <v>7705337</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D97" s="4">
-        <v>4940</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" s="4">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4">
-        <v>0</v>
+      <c r="B97" s="6">
+        <v>7705451</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="6">
+        <v>3</v>
+      </c>
+      <c r="G97" s="6">
+        <v>546</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" s="3">
-        <v>7705337</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="3">
-        <v>4084</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" s="3">
-        <v>0</v>
-      </c>
-      <c r="G98" s="3">
+      <c r="B98" s="4">
+        <v>7705339</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D98" s="4">
+        <v>2030</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="4">
-        <v>3040265</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D99" s="4">
-        <v>4575</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" s="4">
-        <v>67</v>
-      </c>
-      <c r="G99" s="4">
-        <v>1340</v>
+      <c r="B99" s="6">
+        <v>7705341</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D99" s="6">
+        <v>8000</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" s="6">
+        <v>4</v>
+      </c>
+      <c r="G99" s="6">
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" s="3">
-        <v>3001265</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D100" s="3">
-        <v>5010</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="B100" s="4">
+        <v>7705337</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D100" s="4">
+        <v>4940</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" s="4">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="4">
+      <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="4">
-        <v>3002265</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D101" s="4">
-        <v>5082</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" s="4">
-        <v>0</v>
-      </c>
-      <c r="G101" s="4">
+      <c r="B101" s="6">
+        <v>7705337</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D101" s="6">
+        <v>4084</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" s="6">
+        <v>0</v>
+      </c>
+      <c r="G101" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3601,91 +3646,91 @@
       <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" s="3">
-        <v>3002401</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="B102" s="4">
+        <v>3040265</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" s="4">
+        <v>4575</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" s="4">
+        <v>30</v>
+      </c>
+      <c r="G102" s="4">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="5">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6">
+        <v>3617401</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E103" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="4">
-        <v>102</v>
-      </c>
-      <c r="B103" s="4">
-        <v>3006401</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="4">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4">
-        <v>0</v>
+      <c r="F103" s="6">
+        <v>1</v>
+      </c>
+      <c r="G103" s="6">
+        <v>210</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" s="3">
-        <v>3006265</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D104" s="3">
-        <v>5336</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="3">
-        <v>0</v>
+      <c r="B104" s="4">
+        <v>3614401</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="4">
+        <v>1</v>
+      </c>
+      <c r="G104" s="4">
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+      <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="4">
-        <v>3006403</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0</v>
-      </c>
-      <c r="G105" s="4">
+      <c r="B105" s="6">
+        <v>3001265</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D105" s="6">
+        <v>5010</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" s="6">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3693,45 +3738,160 @@
       <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="4">
+        <v>3002265</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106" s="4">
+        <v>5082</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" s="4">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" s="5">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6">
+        <v>3002401</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="6">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4">
+        <v>3006401</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="4">
+        <v>3</v>
+      </c>
+      <c r="G108" s="4">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="5">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6">
+        <v>3006265</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D109" s="6">
+        <v>5336</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F109" s="6">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4">
+        <v>3006403</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="4">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" s="5">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6">
         <v>3006234</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C111" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D111" s="6">
         <v>5532</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" s="3">
+      <c r="E111" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" s="6">
         <v>1</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G111" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="4">
-        <v>106</v>
-      </c>
-      <c r="B107" s="4">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4">
         <v>3084401</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C112" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="4" t="s">
+      <c r="E112" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F107" s="4">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4">
+      <c r="F112" s="4">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCAA41-87A2-456D-9C8B-01F860076800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8BF747-84E2-41F3-B487-AD46AB9CD679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -711,17 +711,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF0F5"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6E6FA"/>
-        <bgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -864,30 +864,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -933,7 +909,7 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -941,16 +917,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1346,45 +1316,45 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>7271111</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>6240</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>7271111</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>10080</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>14</v>
       </c>
     </row>
@@ -1392,45 +1362,45 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>7079401</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>7427401</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1438,45 +1408,45 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>7427213</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>6456</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4">
-        <v>224</v>
+      <c r="E6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="3">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3">
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>7420213</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>6300</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1484,45 +1454,45 @@
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>7420213</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>5812</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="E8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>7209213</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>15540</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="E9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1530,91 +1500,91 @@
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>2968213</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>6008</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2</v>
-      </c>
-      <c r="G10" s="4">
-        <v>28</v>
+      <c r="E10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3">
+        <v>30</v>
+      </c>
+      <c r="G10" s="3">
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>2557195</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>4200</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6">
-        <v>6</v>
-      </c>
-      <c r="G11" s="6">
-        <v>60</v>
+      <c r="E11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4">
+        <v>47</v>
+      </c>
+      <c r="G11" s="4">
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>7232184</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>6020</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4">
-        <v>5</v>
-      </c>
-      <c r="G12" s="4">
-        <v>100</v>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>7638234</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>8400</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>20</v>
       </c>
     </row>
@@ -1622,45 +1592,45 @@
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>7638234</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>7800</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="3">
         <v>3</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>7421234</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>9600</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="E15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1668,45 +1638,45 @@
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>7205222</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>6880</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
+      <c r="E16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="4">
         <v>7330242</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="4">
         <v>670</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4">
         <v>39</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="4">
         <v>390</v>
       </c>
     </row>
@@ -1714,183 +1684,183 @@
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>7330265</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>1300</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="E18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="3">
         <v>20</v>
       </c>
-      <c r="G18" s="4">
+      <c r="G18" s="3">
         <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="4">
         <v>7670213</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
         <v>4860</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="6">
-        <v>5</v>
-      </c>
-      <c r="G19" s="6">
-        <v>70</v>
+      <c r="E19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4">
+        <v>30</v>
+      </c>
+      <c r="G19" s="4">
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>2540199</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="4">
-        <v>18</v>
-      </c>
-      <c r="G20" s="4">
-        <v>151.19999999999999</v>
+      <c r="E20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="3">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3">
+        <v>142.80000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="4">
         <v>7600184</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="4">
         <v>6780</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="6">
-        <v>26</v>
-      </c>
-      <c r="G21" s="6">
-        <v>520</v>
+      <c r="E21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="4">
+        <v>19</v>
+      </c>
+      <c r="G21" s="4">
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>7600203</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>4068</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="4">
-        <v>71</v>
-      </c>
-      <c r="G22" s="4">
-        <v>852</v>
+      <c r="E22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3">
+        <v>53</v>
+      </c>
+      <c r="G22" s="3">
+        <v>636</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="4">
         <v>7688203</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="4">
         <v>4308</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="6">
-        <v>52</v>
-      </c>
-      <c r="G23" s="6">
-        <v>624</v>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46</v>
+      </c>
+      <c r="G23" s="4">
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>7688213</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>5028</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" s="4">
-        <v>7</v>
-      </c>
-      <c r="G24" s="4">
-        <v>98</v>
+      <c r="E24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="3">
+        <v>40</v>
+      </c>
+      <c r="G24" s="3">
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="4">
         <v>7470184</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>6700</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1898,91 +1868,91 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>7470401</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="3">
         <v>1</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="3">
         <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="4">
         <v>2900145</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="4">
         <v>4600</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="6">
-        <v>38</v>
-      </c>
-      <c r="G27" s="6">
-        <v>456</v>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="3">
         <v>2900125</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>5400</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="4">
-        <v>6</v>
-      </c>
-      <c r="G28" s="4">
-        <v>72</v>
+      <c r="E28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="4">
         <v>2900184</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="4">
         <v>7140</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="6">
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4">
         <v>2</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="4">
         <v>40</v>
       </c>
     </row>
@@ -1990,45 +1960,45 @@
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="3">
         <v>2900175</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>3760</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" s="4">
-        <v>11</v>
-      </c>
-      <c r="G30" s="4">
-        <v>110</v>
+      <c r="E30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3</v>
+      </c>
+      <c r="G30" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="4">
         <v>2900103</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="4">
         <v>6600</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="6">
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4">
         <v>1</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="4">
         <v>12</v>
       </c>
     </row>
@@ -2036,45 +2006,45 @@
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>2924229</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>7600</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="E32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="3">
         <v>1</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="4">
         <v>2931184</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="4">
         <v>8700</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="E33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2082,45 +2052,45 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="3">
         <v>2829230</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>8440</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="4">
+      <c r="E34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="3">
         <v>2</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="3">
         <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="4">
         <v>2828229</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="4">
         <v>9280</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="E35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2128,45 +2098,45 @@
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="3">
         <v>2914175</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>6040</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="4">
-        <v>7</v>
-      </c>
-      <c r="G36" s="4">
-        <v>70</v>
+      <c r="E36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="3">
+        <v>5</v>
+      </c>
+      <c r="G36" s="3">
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="4">
         <v>2914165</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="4">
         <v>3180</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="6">
+      <c r="E37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="4">
         <v>5</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="4">
         <v>25</v>
       </c>
     </row>
@@ -2174,45 +2144,45 @@
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="3">
         <v>2909165</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>2200</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="E38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="4">
         <v>2909175</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="4">
         <v>4240</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="6">
+      <c r="E39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="4">
         <v>6</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="4">
         <v>60</v>
       </c>
     </row>
@@ -2220,45 +2190,45 @@
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="3">
         <v>7472184</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>6380</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="4">
-        <v>7</v>
-      </c>
-      <c r="G40" s="4">
-        <v>140</v>
+      <c r="E40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4</v>
+      </c>
+      <c r="G40" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="4">
         <v>7472184</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="4">
         <v>6500</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="6">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="E41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2266,45 +2236,45 @@
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="3">
         <v>2967184</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>11740</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="4">
+      <c r="E42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="3">
         <v>1</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="4">
         <v>2967204</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="4">
         <v>6884</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="6">
+      <c r="E43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="4">
         <v>21</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="4">
         <v>252</v>
       </c>
     </row>
@@ -2312,45 +2282,45 @@
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="3">
         <v>2967111</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>8020</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="4">
-        <v>7</v>
-      </c>
-      <c r="G44" s="4">
-        <v>98</v>
+      <c r="E44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="3">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="4">
         <v>2967111</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="4">
         <v>6372</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="6">
+      <c r="E45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="4">
         <v>10</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="4">
         <v>140</v>
       </c>
     </row>
@@ -2358,137 +2328,137 @@
       <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="3">
         <v>2502401</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="3">
         <v>2</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="3">
         <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="4">
         <v>2502234</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="4">
         <v>6980</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="6">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6">
-        <v>0</v>
+      <c r="E47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4">
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>2502265</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>6830</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="4">
-        <v>3</v>
-      </c>
-      <c r="G48" s="4">
-        <v>60</v>
+      <c r="E48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="4">
         <v>2502184</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="4">
         <v>7100</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" s="6">
-        <v>15</v>
-      </c>
-      <c r="G49" s="6">
-        <v>300</v>
+      <c r="E49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" s="4">
+        <v>6</v>
+      </c>
+      <c r="G49" s="4">
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>2502174</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>7520</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" s="4">
-        <v>6</v>
-      </c>
-      <c r="G50" s="4">
-        <v>120</v>
+      <c r="E50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4</v>
+      </c>
+      <c r="G50" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="4">
         <v>7511184</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="4">
         <v>7800</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" s="6">
-        <v>7</v>
-      </c>
-      <c r="G51" s="6">
+      <c r="E51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="4">
+        <v>7</v>
+      </c>
+      <c r="G51" s="4">
         <v>140</v>
       </c>
     </row>
@@ -2496,45 +2466,45 @@
       <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>7511401</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F52" s="4">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4">
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="4">
         <v>7511251</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="4">
         <v>2763</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="6">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6">
+      <c r="E53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2542,45 +2512,45 @@
       <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="3">
         <v>7705313</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>4500</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="4">
+      <c r="E54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="3">
         <v>8</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="3">
         <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="4">
         <v>7705303</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="4">
         <v>4600</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="6">
+      <c r="E55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="4">
         <v>6</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="4">
         <v>60</v>
       </c>
     </row>
@@ -2588,45 +2558,45 @@
       <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="3">
         <v>7211213</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>6300</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" s="4">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4">
+      <c r="E56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="4">
         <v>2927152</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="4">
         <v>6840</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="6">
+      <c r="E57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="4">
         <v>2</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="4">
         <v>36</v>
       </c>
     </row>
@@ -2634,45 +2604,45 @@
       <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="3">
         <v>2933156</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>6480</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="4">
+      <c r="E58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="3">
         <v>4</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="3">
         <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="4">
         <v>7584401</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F59" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="6">
+      <c r="F59" s="4">
+        <v>0</v>
+      </c>
+      <c r="G59" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2680,45 +2650,45 @@
       <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="3">
         <v>7584175</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="3">
         <v>4060</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="4">
-        <v>25</v>
-      </c>
-      <c r="G60" s="4">
-        <v>250</v>
+      <c r="E60" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="3">
+        <v>13</v>
+      </c>
+      <c r="G60" s="3">
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B61" s="4">
         <v>7584184</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="4">
         <v>7400</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="6">
+      <c r="E61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="4">
         <v>11</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="4">
         <v>220</v>
       </c>
     </row>
@@ -2726,91 +2696,91 @@
       <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="3">
         <v>7577265</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>6600</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="4">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4">
+      <c r="E62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B63" s="4">
         <v>7577401</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F63" s="6">
-        <v>3</v>
-      </c>
-      <c r="G63" s="6">
-        <v>630</v>
+      <c r="F63" s="4">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="3">
         <v>7577256</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="3">
         <v>5025</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="4">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4">
+      <c r="E64" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
-      <c r="B65" s="6">
+      <c r="B65" s="4">
         <v>7577184</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="4">
         <v>6900</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" s="6">
-        <v>7</v>
-      </c>
-      <c r="G65" s="6">
+      <c r="E65" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" s="4">
+        <v>7</v>
+      </c>
+      <c r="G65" s="4">
         <v>140</v>
       </c>
     </row>
@@ -2818,91 +2788,91 @@
       <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="3">
         <v>7577174</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="3">
         <v>7320</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" s="4">
+      <c r="E66" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="3">
         <v>5</v>
       </c>
-      <c r="G66" s="4">
+      <c r="G66" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>66</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="4">
         <v>7577234</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="4">
         <v>6780</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="6">
-        <v>0</v>
+      <c r="E67" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="4">
+        <v>3</v>
+      </c>
+      <c r="G67" s="4">
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="3">
         <v>7577240</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="3">
         <v>6780</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" s="4">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4">
+      <c r="E68" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>68</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B69" s="4">
         <v>7577251</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="4">
         <v>2513</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" s="6">
-        <v>0</v>
-      </c>
-      <c r="G69" s="6">
+      <c r="E69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="4">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2910,91 +2880,91 @@
       <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="3">
         <v>1404184</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="3">
         <v>6800</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4">
+      <c r="E70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>70</v>
       </c>
-      <c r="B71" s="6">
+      <c r="B71" s="4">
         <v>1404184</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="4">
         <v>7100</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="6">
-        <v>2</v>
-      </c>
-      <c r="G71" s="6">
-        <v>40</v>
+      <c r="E71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="3">
         <v>1404234</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="3">
         <v>7100</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" s="4">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4">
+      <c r="E72" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>72</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B73" s="4">
         <v>7436253</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="4">
         <v>6175</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" s="6">
-        <v>0</v>
-      </c>
-      <c r="G73" s="6">
+      <c r="E73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" s="4">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3002,45 +2972,45 @@
       <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="3">
         <v>7436250</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="3">
         <v>3113</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" s="4">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4">
+      <c r="E74" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="5">
+      <c r="A75" s="4">
         <v>74</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B75" s="4">
         <v>7556234</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="4">
         <v>6900</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" s="6">
-        <v>0</v>
-      </c>
-      <c r="G75" s="6">
+      <c r="E75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F75" s="4">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3048,45 +3018,45 @@
       <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="3">
         <v>7556184</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>7100</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="4">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4">
+      <c r="E76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <v>76</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B77" s="4">
         <v>7556241</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="4">
         <v>3400</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" s="6">
-        <v>0</v>
-      </c>
-      <c r="G77" s="6">
+      <c r="E77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" s="4">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3094,45 +3064,45 @@
       <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="3">
         <v>7556253</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="3">
         <v>5025</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" s="4">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
+      <c r="E78" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="5">
+      <c r="A79" s="4">
         <v>78</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B79" s="4">
         <v>7556250</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="4">
         <v>2563</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" s="6">
+      <c r="E79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F79" s="4">
         <v>3</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="4">
         <v>22.5</v>
       </c>
     </row>
@@ -3140,45 +3110,45 @@
       <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="3">
         <v>7489253</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="3">
         <v>5675</v>
       </c>
-      <c r="E80" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" s="4">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4">
+      <c r="E80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="5">
+      <c r="A81" s="4">
         <v>80</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B81" s="4">
         <v>7489265</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D81" s="4">
         <v>7500</v>
       </c>
-      <c r="E81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" s="6">
-        <v>0</v>
-      </c>
-      <c r="G81" s="6">
+      <c r="E81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F81" s="4">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3186,45 +3156,45 @@
       <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="3">
         <v>7489184</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="3">
         <v>7900</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" s="4">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4">
+      <c r="E82" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0</v>
+      </c>
+      <c r="G82" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="5">
+      <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B83" s="4">
         <v>7489234</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="4">
         <v>7700</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="6">
+      <c r="E83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="4">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3232,45 +3202,45 @@
       <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="3">
         <v>2889156</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>6840</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" s="4">
-        <v>3</v>
-      </c>
-      <c r="G84" s="4">
-        <v>48</v>
+      <c r="E84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" s="3">
+        <v>2</v>
+      </c>
+      <c r="G84" s="3">
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B85" s="4">
         <v>7485242</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="4">
         <v>2890</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="6">
+      <c r="E85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" s="4">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3278,367 +3248,367 @@
       <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="3">
         <v>7485265</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="3">
         <v>5740</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" s="4">
-        <v>3</v>
-      </c>
-      <c r="G86" s="4">
-        <v>60</v>
+      <c r="E86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B87" s="4">
         <v>7485184</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="4">
         <v>6040</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" s="6">
-        <v>13</v>
-      </c>
-      <c r="G87" s="6">
-        <v>260</v>
+      <c r="E87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" s="4">
+        <v>6</v>
+      </c>
+      <c r="G87" s="4">
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="3">
         <v>7485401</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F88" s="4">
-        <v>0</v>
-      </c>
-      <c r="G88" s="4">
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <v>88</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B89" s="4">
         <v>7485174</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="4">
         <v>6240</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" s="6">
-        <v>22</v>
-      </c>
-      <c r="G89" s="6">
-        <v>440</v>
+      <c r="E89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F89" s="4">
+        <v>21</v>
+      </c>
+      <c r="G89" s="4">
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="3">
         <v>7485234</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="3">
         <v>6020</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" s="4">
-        <v>5</v>
-      </c>
-      <c r="G90" s="4">
-        <v>100</v>
+      <c r="E90" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="5">
+      <c r="A91" s="4">
         <v>90</v>
       </c>
-      <c r="B91" s="6">
+      <c r="B91" s="4">
         <v>7485251</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="4">
         <v>2176</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" s="6">
-        <v>6</v>
-      </c>
-      <c r="G91" s="6">
-        <v>45</v>
+      <c r="E91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" s="4">
+        <v>3</v>
+      </c>
+      <c r="G91" s="4">
+        <v>22.5</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="3">
         <v>7208271</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E92" s="4" t="s">
+      <c r="E92" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="4">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4">
+      <c r="F92" s="3">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="5">
+      <c r="A93" s="4">
         <v>92</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B93" s="4">
         <v>4906175</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="4">
         <v>3960</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" s="6">
-        <v>0</v>
-      </c>
-      <c r="G93" s="6">
-        <v>0</v>
+      <c r="E93" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" s="4">
+        <v>4</v>
+      </c>
+      <c r="G93" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="3">
         <v>4906184</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="3">
         <v>7500</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" s="4">
-        <v>4</v>
-      </c>
-      <c r="G94" s="4">
-        <v>80</v>
+      <c r="E94" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="5">
+      <c r="A95" s="4">
         <v>94</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B95" s="4">
         <v>7742451</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="E95" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F95" s="6">
-        <v>1</v>
-      </c>
-      <c r="G95" s="6">
-        <v>182</v>
+      <c r="F95" s="4">
+        <v>0</v>
+      </c>
+      <c r="G95" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="3">
         <v>7742341</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="3">
         <v>9700</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" s="4">
-        <v>15</v>
-      </c>
-      <c r="G96" s="4">
-        <v>300</v>
+      <c r="E96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <v>96</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="4">
         <v>7705451</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E97" s="6" t="s">
+      <c r="E97" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F97" s="6">
-        <v>3</v>
-      </c>
-      <c r="G97" s="6">
-        <v>546</v>
+      <c r="F97" s="4">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="3">
         <v>7705339</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>2030</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" s="4">
-        <v>0</v>
-      </c>
-      <c r="G98" s="4">
+      <c r="E98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <v>98</v>
       </c>
-      <c r="B99" s="6">
+      <c r="B99" s="4">
         <v>7705341</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="4">
         <v>8000</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" s="6">
-        <v>4</v>
-      </c>
-      <c r="G99" s="6">
-        <v>80</v>
+      <c r="E99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" s="4">
+        <v>2</v>
+      </c>
+      <c r="G99" s="4">
+        <v>40</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="3">
         <v>7705337</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="3">
         <v>4940</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" s="4">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4">
+      <c r="E100" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <v>100</v>
       </c>
-      <c r="B101" s="6">
+      <c r="B101" s="4">
         <v>7705337</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="4">
         <v>4084</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" s="6">
-        <v>0</v>
-      </c>
-      <c r="G101" s="6">
+      <c r="E101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" s="4">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3646,91 +3616,91 @@
       <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="3">
         <v>3040265</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="3">
         <v>4575</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" s="4">
-        <v>30</v>
-      </c>
-      <c r="G102" s="4">
-        <v>600</v>
+      <c r="E102" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" s="3">
+        <v>24</v>
+      </c>
+      <c r="G102" s="3">
+        <v>480</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <v>102</v>
       </c>
-      <c r="B103" s="6">
+      <c r="B103" s="4">
         <v>3617401</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="6" t="s">
+      <c r="E103" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F103" s="6">
-        <v>1</v>
-      </c>
-      <c r="G103" s="6">
-        <v>210</v>
+      <c r="F103" s="4">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="3">
         <v>3614401</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E104" s="4" t="s">
+      <c r="E104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F104" s="4">
-        <v>1</v>
-      </c>
-      <c r="G104" s="4">
-        <v>210</v>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <v>104</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="4">
         <v>3001265</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D105" s="4">
         <v>5010</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" s="6">
-        <v>0</v>
-      </c>
-      <c r="G105" s="6">
+      <c r="E105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" s="4">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3738,45 +3708,45 @@
       <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="3">
         <v>3002265</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="3">
         <v>5082</v>
       </c>
-      <c r="E106" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" s="4">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4">
+      <c r="E106" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <v>106</v>
       </c>
-      <c r="B107" s="6">
+      <c r="B107" s="4">
         <v>3002401</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E107" s="6" t="s">
+      <c r="E107" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F107" s="6">
-        <v>0</v>
-      </c>
-      <c r="G107" s="6">
+      <c r="F107" s="4">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3784,45 +3754,45 @@
       <c r="A108" s="3">
         <v>107</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="3">
         <v>3006401</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E108" s="4" t="s">
+      <c r="E108" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="4">
-        <v>3</v>
-      </c>
-      <c r="G108" s="4">
-        <v>630</v>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <v>108</v>
       </c>
-      <c r="B109" s="6">
+      <c r="B109" s="4">
         <v>3006265</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D109" s="4">
         <v>5336</v>
       </c>
-      <c r="E109" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F109" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="6">
+      <c r="E109" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F109" s="4">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4">
         <v>0</v>
       </c>
     </row>
@@ -3830,45 +3800,45 @@
       <c r="A110" s="3">
         <v>109</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="3">
         <v>3006403</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F110" s="4">
-        <v>0</v>
-      </c>
-      <c r="G110" s="4">
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <v>110</v>
       </c>
-      <c r="B111" s="6">
+      <c r="B111" s="4">
         <v>3006234</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D111" s="6">
+      <c r="D111" s="4">
         <v>5532</v>
       </c>
-      <c r="E111" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" s="6">
+      <c r="E111" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" s="4">
         <v>1</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G111" s="4">
         <v>20</v>
       </c>
     </row>
@@ -3876,22 +3846,22 @@
       <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="3">
         <v>3084401</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="E112" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F112" s="4">
-        <v>0</v>
-      </c>
-      <c r="G112" s="4">
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Stock Available from Not Received physical product/Current Stock.xlsx
+++ b/Stock Available from Not Received physical product/Current Stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Stock Available from Not Received physical product\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8BF747-84E2-41F3-B487-AD46AB9CD679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D467D9DF-5FC6-4968-A63B-2C34E5C7FF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4815B4F6-FE69-4A17-8E4F-70DF6941189F}"/>
   </bookViews>
@@ -1312,7 +1312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1421,10 +1421,10 @@
         <v>7</v>
       </c>
       <c r="F6" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
-        <v>140</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1513,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1536,10 +1536,10 @@
         <v>7</v>
       </c>
       <c r="F11" s="4">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1565,7 +1565,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1720,10 +1720,10 @@
         <v>7</v>
       </c>
       <c r="F19" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1789,10 +1789,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="3">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G22" s="3">
-        <v>636</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1812,10 +1812,10 @@
         <v>7</v>
       </c>
       <c r="F23" s="4">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="G23" s="4">
-        <v>552</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1835,13 +1835,13 @@
         <v>7</v>
       </c>
       <c r="F24" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G24" s="3">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1881,13 +1881,13 @@
         <v>11</v>
       </c>
       <c r="F26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2157,13 +2157,13 @@
         <v>7</v>
       </c>
       <c r="F38" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2778,13 +2778,13 @@
         <v>7</v>
       </c>
       <c r="F65" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G65" s="4">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -3284,10 +3284,10 @@
         <v>7</v>
       </c>
       <c r="F87" s="4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G87" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3330,10 +3330,10 @@
         <v>7</v>
       </c>
       <c r="F89" s="4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
